--- a/URIARTE 630/Diciembre/EXPENSAS-Diciembre.xlsx
+++ b/URIARTE 630/Diciembre/EXPENSAS-Diciembre.xlsx
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\URIARTE 630\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD41A5B-6710-4B00-95C7-1484DEF2F79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AED4951-4E86-4D1D-985B-0415AC00FDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="prorrateo " sheetId="1" r:id="rId1"/>
-    <sheet name="detalle y gastos" sheetId="3" r:id="rId2"/>
+    <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
+    <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'prorrateo '!$A$1:$M$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
   <si>
     <t>UF</t>
   </si>
@@ -246,6 +246,12 @@
   </si>
   <si>
     <t>Servisur - Sellado de artefacto de iluminacion</t>
+  </si>
+  <si>
+    <t>Recarga Matafuegos - MEGASEC</t>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
   </si>
 </sst>
 </file>
@@ -259,7 +265,7 @@
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,13 +375,6 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1180,7 +1179,29 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1196,12 +1217,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1211,23 +1226,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1240,8 +1238,11 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1605,58 +1606,499 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:G65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="126" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="127"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="130">
+        <f>71833+71833*20%</f>
+        <v>86199.6</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="31">
+        <v>-658663.76281600632</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="45"/>
+      <c r="C13" s="130">
+        <v>4519.7749999999996</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="101" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="102">
+        <f>'prorrateo '!F10</f>
+        <v>755657.75826400006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="45"/>
+      <c r="C14" s="43">
+        <v>95606.720000000001</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="101" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="103">
+        <f>-C25</f>
+        <v>-620524.13500000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="43">
+        <v>140555</v>
+      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="104"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="53"/>
+      <c r="C16" s="130">
+        <v>28281.4</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="104"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="45"/>
+      <c r="C17" s="130">
+        <v>66605.47</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="104"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="52"/>
+      <c r="C18" s="130">
+        <v>157756.17000000001</v>
+      </c>
+      <c r="E18" s="101"/>
+      <c r="F18" s="104"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="45"/>
+      <c r="C19" s="130">
+        <v>0</v>
+      </c>
+      <c r="E19" s="101"/>
+      <c r="F19" s="104"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="47"/>
+      <c r="C20" s="131">
+        <f>SUM(C12:C19)</f>
+        <v>579524.13500000001</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="33">
+        <f>SUM(F12:F18)</f>
+        <v>-523530.13955200627</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="45"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="45"/>
+      <c r="C22" s="43">
+        <v>20000</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="129" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="129"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="45"/>
+      <c r="C23" s="43">
+        <v>21000</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="129"/>
+      <c r="F23" s="129"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="44">
+        <f>SUM(C21:C23)</f>
+        <v>41000</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="75">
+        <f>+C24+C20</f>
+        <v>620524.13500000001</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="129"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="76"/>
+      <c r="E26" s="129"/>
+      <c r="F26" s="129"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="129"/>
+      <c r="F27" s="129"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="77"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="78">
+        <v>0</v>
+      </c>
+      <c r="E29" s="129"/>
+      <c r="F29" s="129"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="78">
+        <v>0</v>
+      </c>
+      <c r="E30" s="129"/>
+      <c r="F30" s="129"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="79"/>
+      <c r="E31" s="129"/>
+      <c r="F31" s="129"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="128"/>
+      <c r="B32" s="128"/>
+      <c r="C32" s="78"/>
+      <c r="E32" s="129"/>
+      <c r="F32" s="129"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="29"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="78">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="50">
+        <f>SUM(C29:C33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="78"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="80">
+        <f>C35+C25</f>
+        <v>620524.13500000001</v>
+      </c>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="37"/>
+      <c r="C37" s="50">
+        <f>+C25+C34</f>
+        <v>620524.13500000001</v>
+      </c>
+      <c r="E37" s="10"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="12"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="13"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E22:F32"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T118"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="0.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="0.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="123" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de DICIEMBRE</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
       <c r="D1" s="86"/>
       <c r="E1" s="87" t="s">
         <v>34</v>
       </c>
       <c r="F1" s="86"/>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="109">
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="121">
         <f>Q1</f>
-        <v>667935.08499999996</v>
-      </c>
-      <c r="M1" s="110"/>
+        <v>620524.13500000001</v>
+      </c>
+      <c r="M1" s="122"/>
       <c r="Q1">
-        <v>667935.08499999996</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+        <v>620524.13500000001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 15/01</v>
@@ -1678,7 +2120,7 @@
         <v>413723.43999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="89" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +2161,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="89"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
@@ -1755,7 +2197,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="89">
         <v>1</v>
       </c>
@@ -1769,23 +2211,26 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>162655.50505000001</v>
-      </c>
-      <c r="F5" s="9"/>
+        <v>329248</v>
+      </c>
+      <c r="F5" s="43">
+        <f>E5</f>
+        <v>329248</v>
+      </c>
       <c r="G5" s="84">
         <f>E5-F5</f>
-        <v>162655.50505000001</v>
+        <v>0</v>
       </c>
       <c r="H5" s="85">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>13663.062424200001</v>
+        <v>0</v>
       </c>
       <c r="I5" s="9">
         <v>0</v>
       </c>
       <c r="J5" s="23">
         <f>L$1*B5</f>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="K5" s="9">
         <f>K$2*D5</f>
@@ -1793,14 +2238,14 @@
       </c>
       <c r="L5" s="9">
         <f>J5+K5+H5+G5</f>
-        <v>316584.93532419996</v>
+        <v>130310.06835</v>
       </c>
       <c r="M5" s="91">
         <f>L5+L5*4%</f>
-        <v>329248.33273716795</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>135522.47108399999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="89">
         <v>2</v>
       </c>
@@ -1814,26 +2259,23 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>128877</v>
-      </c>
-      <c r="F6" s="9">
-        <f>E6</f>
-        <v>128877</v>
-      </c>
+        <v>106869.6136</v>
+      </c>
+      <c r="F6" s="43"/>
       <c r="G6" s="84">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
-        <v>0</v>
+        <v>106869.6136</v>
       </c>
       <c r="H6" s="85">
         <f t="shared" ref="H6:H9" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>0</v>
+        <v>8977.0475423999997</v>
       </c>
       <c r="I6" s="9">
         <v>0</v>
       </c>
       <c r="J6" s="23">
         <f>L$1*B6</f>
-        <v>106869.6136</v>
+        <v>99283.861600000004</v>
       </c>
       <c r="K6" s="9">
         <f>K$2*D6</f>
@@ -1841,14 +2283,14 @@
       </c>
       <c r="L6" s="9">
         <f t="shared" ref="L6:L9" si="2">J6+K6+H6+G6</f>
-        <v>106869.6136</v>
+        <v>215130.5227424</v>
       </c>
       <c r="M6" s="91">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>111144.39814399999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>223735.74365209602</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="89">
         <v>3</v>
       </c>
@@ -1860,11 +2302,11 @@
       </c>
       <c r="D7" s="49"/>
       <c r="E7" s="23">
-        <v>162644.66505000001</v>
-      </c>
-      <c r="F7" s="9">
+        <v>145877.02256399998</v>
+      </c>
+      <c r="F7" s="43">
         <f>E7</f>
-        <v>162644.66505000001</v>
+        <v>145877.02256399998</v>
       </c>
       <c r="G7" s="84">
         <f t="shared" si="0"/>
@@ -1877,21 +2319,21 @@
       <c r="I7" s="9"/>
       <c r="J7" s="23">
         <f>L$1*B7</f>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="2"/>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="M7" s="91">
         <f t="shared" si="3"/>
-        <v>145877.02256399998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>135522.47108399999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="89">
         <v>4</v>
       </c>
@@ -1903,11 +2345,11 @@
       </c>
       <c r="D8" s="49"/>
       <c r="E8" s="23">
-        <v>162644.66505000001</v>
-      </c>
-      <c r="F8" s="9">
+        <v>140266.36784999998</v>
+      </c>
+      <c r="F8" s="43">
         <f>E8</f>
-        <v>162644.66505000001</v>
+        <v>140266.36784999998</v>
       </c>
       <c r="G8" s="84">
         <f t="shared" si="0"/>
@@ -1920,21 +2362,21 @@
       <c r="I8" s="9"/>
       <c r="J8" s="23">
         <f>L$1*B8</f>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="2"/>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="M8" s="91">
         <f t="shared" si="3"/>
-        <v>145877.02256399998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>135522.47108399999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="89">
         <v>5</v>
       </c>
@@ -1946,10 +2388,11 @@
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="23">
-        <v>305328</v>
-      </c>
-      <c r="F9" s="9">
-        <v>305328</v>
+        <v>140266.36784999998</v>
+      </c>
+      <c r="F9" s="43">
+        <f>E9</f>
+        <v>140266.36784999998</v>
       </c>
       <c r="G9" s="84">
         <f t="shared" si="0"/>
@@ -1962,21 +2405,21 @@
       <c r="I9" s="9"/>
       <c r="J9" s="23">
         <f>L$1*B9</f>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="2"/>
-        <v>140266.36784999998</v>
+        <v>130310.06835</v>
       </c>
       <c r="M9" s="91">
         <f t="shared" si="3"/>
-        <v>145877.02256399998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>135522.47108399999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="92" t="s">
         <v>7</v>
       </c>
@@ -1991,19 +2434,19 @@
       </c>
       <c r="E10" s="96">
         <f>SUM(E5:E9)</f>
-        <v>922149.83515000006</v>
+        <v>862527.3718640001</v>
       </c>
       <c r="F10" s="96">
         <f>SUM(F5:F9)</f>
-        <v>759494.33010000002</v>
+        <v>755657.75826400006</v>
       </c>
       <c r="G10" s="96">
         <f t="shared" si="4"/>
-        <v>162655.50505000001</v>
+        <v>106869.6136</v>
       </c>
       <c r="H10" s="96">
         <f t="shared" si="4"/>
-        <v>13663.062424200001</v>
+        <v>8977.0475423999997</v>
       </c>
       <c r="I10" s="97">
         <f t="shared" si="4"/>
@@ -2011,7 +2454,7 @@
       </c>
       <c r="J10" s="98">
         <f>SUM(J5:J9)</f>
-        <v>667935.08499999996</v>
+        <v>620524.13500000001</v>
       </c>
       <c r="K10" s="98">
         <f t="shared" si="4"/>
@@ -2019,56 +2462,56 @@
       </c>
       <c r="L10" s="96">
         <f>SUM(L5:L9)</f>
-        <v>844253.65247419989</v>
+        <v>736370.79614240001</v>
       </c>
       <c r="M10" s="99">
         <f>SUM(M5:M9)</f>
-        <v>878023.79857316788</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="117"/>
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="117"/>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>765825.62798809586</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
+      <c r="M11" s="125"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="118" t="s">
+    <row r="13" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="114"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="110"/>
       <c r="J14" s="55"/>
       <c r="K14" s="56"/>
       <c r="L14" s="60"/>
     </row>
-    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="120" t="s">
+    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="114"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="110"/>
       <c r="J15" s="57"/>
       <c r="K15" s="58"/>
       <c r="L15" s="60"/>
@@ -2079,7 +2522,7 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="55"/>
       <c r="D16" s="59"/>
       <c r="E16" s="59"/>
@@ -2099,7 +2542,7 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C17" s="57" t="s">
         <v>47</v>
       </c>
@@ -2121,7 +2564,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C18" s="61"/>
       <c r="D18" s="62"/>
       <c r="E18" s="62"/>
@@ -2139,21 +2582,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="121" t="s">
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="123"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="117"/>
       <c r="J19" s="57"/>
       <c r="K19" s="58"/>
       <c r="L19" s="60"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C20" s="57"/>
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
@@ -2171,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C21" s="57" t="s">
         <v>49</v>
       </c>
@@ -2186,13 +2629,13 @@
       </c>
       <c r="H21" s="64"/>
       <c r="I21" s="58"/>
-      <c r="J21" s="124" t="s">
+      <c r="J21" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="K21" s="125"/>
+      <c r="K21" s="106"/>
       <c r="L21" s="73"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C22" s="57" t="s">
         <v>52</v>
       </c>
@@ -2211,7 +2654,7 @@
       <c r="K22" s="58"/>
       <c r="L22" s="60"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" s="57"/>
       <c r="D23" s="60"/>
       <c r="E23" s="60"/>
@@ -2219,11 +2662,11 @@
       <c r="G23" s="60"/>
       <c r="H23" s="60"/>
       <c r="I23" s="58"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="125"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="106"/>
       <c r="L23" s="73"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C24" s="71" t="s">
         <v>55</v>
       </c>
@@ -2233,14 +2676,14 @@
       <c r="G24" s="60"/>
       <c r="H24" s="70">
         <f>L$1/5</f>
-        <v>133587.01699999999</v>
+        <v>124104.827</v>
       </c>
       <c r="I24" s="58"/>
       <c r="J24" s="57"/>
       <c r="K24" s="58"/>
       <c r="L24" s="60"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C25" s="72" t="s">
         <v>38</v>
       </c>
@@ -2257,7 +2700,7 @@
       <c r="K25" s="58"/>
       <c r="L25" s="60"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C26" s="72" t="s">
         <v>36</v>
       </c>
@@ -2274,7 +2717,7 @@
       <c r="K26" s="58"/>
       <c r="L26" s="60"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C27" s="72" t="s">
         <v>39</v>
       </c>
@@ -2291,7 +2734,7 @@
       <c r="K27" s="58"/>
       <c r="L27" s="60"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="72" t="s">
         <v>37</v>
       </c>
@@ -2308,7 +2751,7 @@
       <c r="K28" s="58"/>
       <c r="L28" s="60"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="D29" s="60"/>
       <c r="E29" s="60"/>
       <c r="F29" s="60"/>
@@ -2319,7 +2762,7 @@
       <c r="K29" s="58"/>
       <c r="L29" s="60"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C30" s="72" t="s">
         <v>43</v>
       </c>
@@ -2336,7 +2779,7 @@
       <c r="K30" s="58"/>
       <c r="L30" s="60"/>
     </row>
-    <row r="31" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="57"/>
       <c r="D31" s="60"/>
       <c r="E31" s="60"/>
@@ -2348,55 +2791,55 @@
       <c r="K31" s="67"/>
       <c r="L31" s="60"/>
     </row>
-    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="111" t="s">
+    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="112"/>
-      <c r="E32" s="112"/>
-      <c r="F32" s="112"/>
-      <c r="G32" s="112"/>
-      <c r="H32" s="113">
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="109">
         <f>SUM(H24:H31)</f>
-        <v>178953.3995</v>
-      </c>
-      <c r="I32" s="114"/>
+        <v>169471.2095</v>
+      </c>
+      <c r="I32" s="110"/>
       <c r="J32" s="68"/>
       <c r="K32" s="69"/>
       <c r="L32" s="60"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="118" t="s">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="114"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="110"/>
       <c r="J36" s="55"/>
       <c r="K36" s="56"/>
       <c r="L36" s="60"/>
     </row>
-    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="120" t="s">
+    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="119"/>
-      <c r="I37" s="114"/>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="110"/>
       <c r="J37" s="57"/>
       <c r="K37" s="58"/>
       <c r="L37" s="60"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C38" s="55"/>
       <c r="D38" s="59"/>
       <c r="E38" s="59"/>
@@ -2410,7 +2853,7 @@
       <c r="K38" s="58"/>
       <c r="L38" s="60"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C39" s="57" t="s">
         <v>47</v>
       </c>
@@ -2427,7 +2870,7 @@
       <c r="K39" s="58"/>
       <c r="L39" s="60"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C40" s="61"/>
       <c r="D40" s="62"/>
       <c r="E40" s="62"/>
@@ -2439,21 +2882,21 @@
       <c r="K40" s="58"/>
       <c r="L40" s="60"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="121" t="s">
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="122"/>
-      <c r="E41" s="122"/>
-      <c r="F41" s="122"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="122"/>
-      <c r="I41" s="123"/>
+      <c r="D41" s="116"/>
+      <c r="E41" s="116"/>
+      <c r="F41" s="116"/>
+      <c r="G41" s="116"/>
+      <c r="H41" s="116"/>
+      <c r="I41" s="117"/>
       <c r="J41" s="57"/>
       <c r="K41" s="58"/>
       <c r="L41" s="60"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C42" s="57"/>
       <c r="D42" s="60"/>
       <c r="E42" s="60"/>
@@ -2465,7 +2908,7 @@
       <c r="K42" s="58"/>
       <c r="L42" s="60"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C43" s="57" t="s">
         <v>49</v>
       </c>
@@ -2480,13 +2923,13 @@
       </c>
       <c r="H43" s="64"/>
       <c r="I43" s="58"/>
-      <c r="J43" s="124" t="s">
+      <c r="J43" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="K43" s="125"/>
+      <c r="K43" s="106"/>
       <c r="L43" s="73"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C44" s="57" t="s">
         <v>52</v>
       </c>
@@ -2505,7 +2948,7 @@
       <c r="K44" s="58"/>
       <c r="L44" s="60"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="57"/>
       <c r="D45" s="60"/>
       <c r="E45" s="60"/>
@@ -2513,11 +2956,11 @@
       <c r="G45" s="60"/>
       <c r="H45" s="60"/>
       <c r="I45" s="58"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="125"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="106"/>
       <c r="L45" s="73"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="57" t="s">
         <v>55</v>
       </c>
@@ -2527,14 +2970,14 @@
       <c r="G46" s="60"/>
       <c r="H46" s="70">
         <f>L$1/5</f>
-        <v>133587.01699999999</v>
+        <v>124104.827</v>
       </c>
       <c r="I46" s="58"/>
       <c r="J46" s="57"/>
       <c r="K46" s="58"/>
       <c r="L46" s="60"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="57"/>
       <c r="D47" s="60"/>
       <c r="E47" s="60"/>
@@ -2546,7 +2989,7 @@
       <c r="K47" s="58"/>
       <c r="L47" s="60"/>
     </row>
-    <row r="48" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C48" s="57"/>
       <c r="D48" s="60"/>
       <c r="E48" s="60"/>
@@ -2558,54 +3001,54 @@
       <c r="K48" s="67"/>
       <c r="L48" s="60"/>
     </row>
-    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="111" t="s">
+    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="112"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="112"/>
-      <c r="H49" s="113">
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="109">
         <f>M6</f>
-        <v>111144.39814399999</v>
-      </c>
-      <c r="I49" s="114"/>
+        <v>223735.74365209602</v>
+      </c>
+      <c r="I49" s="110"/>
       <c r="J49" s="68"/>
       <c r="K49" s="69"/>
       <c r="L49" s="60"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="118" t="s">
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
-      <c r="I52" s="114"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="113"/>
+      <c r="F52" s="113"/>
+      <c r="G52" s="113"/>
+      <c r="H52" s="113"/>
+      <c r="I52" s="110"/>
       <c r="J52" s="55"/>
       <c r="K52" s="56"/>
       <c r="L52" s="60"/>
     </row>
-    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="120" t="s">
+    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
-      <c r="H53" s="119"/>
-      <c r="I53" s="114"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="113"/>
+      <c r="F53" s="113"/>
+      <c r="G53" s="113"/>
+      <c r="H53" s="113"/>
+      <c r="I53" s="110"/>
       <c r="J53" s="57"/>
       <c r="K53" s="58"/>
       <c r="L53" s="60"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" s="55"/>
       <c r="D54" s="59"/>
       <c r="E54" s="59"/>
@@ -2619,7 +3062,7 @@
       <c r="K54" s="58"/>
       <c r="L54" s="60"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="57" t="s">
         <v>47</v>
       </c>
@@ -2636,7 +3079,7 @@
       <c r="K55" s="58"/>
       <c r="L55" s="60"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" s="61"/>
       <c r="D56" s="62"/>
       <c r="E56" s="62"/>
@@ -2648,21 +3091,21 @@
       <c r="K56" s="58"/>
       <c r="L56" s="60"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="121" t="s">
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="122"/>
-      <c r="E57" s="122"/>
-      <c r="F57" s="122"/>
-      <c r="G57" s="122"/>
-      <c r="H57" s="122"/>
-      <c r="I57" s="123"/>
+      <c r="D57" s="116"/>
+      <c r="E57" s="116"/>
+      <c r="F57" s="116"/>
+      <c r="G57" s="116"/>
+      <c r="H57" s="116"/>
+      <c r="I57" s="117"/>
       <c r="J57" s="57"/>
       <c r="K57" s="58"/>
       <c r="L57" s="60"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" s="57"/>
       <c r="D58" s="60"/>
       <c r="E58" s="60"/>
@@ -2674,7 +3117,7 @@
       <c r="K58" s="58"/>
       <c r="L58" s="60"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" s="57" t="s">
         <v>49</v>
       </c>
@@ -2689,13 +3132,13 @@
       </c>
       <c r="H59" s="64"/>
       <c r="I59" s="58"/>
-      <c r="J59" s="124" t="s">
+      <c r="J59" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="K59" s="125"/>
+      <c r="K59" s="106"/>
       <c r="L59" s="73"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" s="57" t="s">
         <v>52</v>
       </c>
@@ -2714,7 +3157,7 @@
       <c r="K60" s="58"/>
       <c r="L60" s="60"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C61" s="57"/>
       <c r="D61" s="60"/>
       <c r="E61" s="60"/>
@@ -2722,11 +3165,11 @@
       <c r="G61" s="60"/>
       <c r="H61" s="60"/>
       <c r="I61" s="58"/>
-      <c r="J61" s="126"/>
-      <c r="K61" s="125"/>
+      <c r="J61" s="105"/>
+      <c r="K61" s="106"/>
       <c r="L61" s="73"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" s="57" t="s">
         <v>55</v>
       </c>
@@ -2736,14 +3179,14 @@
       <c r="G62" s="60"/>
       <c r="H62" s="70">
         <f>L$1/5</f>
-        <v>133587.01699999999</v>
+        <v>124104.827</v>
       </c>
       <c r="I62" s="58"/>
       <c r="J62" s="57"/>
       <c r="K62" s="58"/>
       <c r="L62" s="60"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="72" t="s">
         <v>38</v>
       </c>
@@ -2760,7 +3203,7 @@
       <c r="K63" s="58"/>
       <c r="L63" s="60"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" s="72" t="s">
         <v>36</v>
       </c>
@@ -2777,7 +3220,7 @@
       <c r="K64" s="58"/>
       <c r="L64" s="60"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C65" s="72" t="s">
         <v>39</v>
       </c>
@@ -2794,7 +3237,7 @@
       <c r="K65" s="58"/>
       <c r="L65" s="60"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" s="72" t="s">
         <v>37</v>
       </c>
@@ -2811,7 +3254,7 @@
       <c r="K66" s="58"/>
       <c r="L66" s="60"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D67" s="60"/>
       <c r="E67" s="60"/>
       <c r="F67" s="60"/>
@@ -2822,7 +3265,7 @@
       <c r="K67" s="58"/>
       <c r="L67" s="60"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="72" t="s">
         <v>43</v>
       </c>
@@ -2839,7 +3282,7 @@
       <c r="K68" s="58"/>
       <c r="L68" s="60"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="57"/>
       <c r="D69" s="60"/>
       <c r="E69" s="60"/>
@@ -2851,7 +3294,7 @@
       <c r="K69" s="58"/>
       <c r="L69" s="60"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C70" s="57"/>
       <c r="D70" s="60"/>
       <c r="E70" s="60"/>
@@ -2863,7 +3306,7 @@
       <c r="K70" s="58"/>
       <c r="L70" s="60"/>
     </row>
-    <row r="71" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C71" s="57"/>
       <c r="D71" s="60"/>
       <c r="E71" s="60"/>
@@ -2875,55 +3318,55 @@
       <c r="K71" s="67"/>
       <c r="L71" s="60"/>
     </row>
-    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="111" t="s">
+    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="D72" s="112"/>
-      <c r="E72" s="112"/>
-      <c r="F72" s="112"/>
-      <c r="G72" s="112"/>
-      <c r="H72" s="113">
+      <c r="D72" s="108"/>
+      <c r="E72" s="108"/>
+      <c r="F72" s="108"/>
+      <c r="G72" s="108"/>
+      <c r="H72" s="109">
         <f>SUM(H62:H71)</f>
-        <v>178953.3995</v>
-      </c>
-      <c r="I72" s="114"/>
+        <v>169471.2095</v>
+      </c>
+      <c r="I72" s="110"/>
       <c r="J72" s="68"/>
       <c r="K72" s="69"/>
       <c r="L72" s="60"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="118" t="s">
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D76" s="119"/>
-      <c r="E76" s="119"/>
-      <c r="F76" s="119"/>
-      <c r="G76" s="119"/>
-      <c r="H76" s="119"/>
-      <c r="I76" s="114"/>
+      <c r="D76" s="113"/>
+      <c r="E76" s="113"/>
+      <c r="F76" s="113"/>
+      <c r="G76" s="113"/>
+      <c r="H76" s="113"/>
+      <c r="I76" s="110"/>
       <c r="J76" s="55"/>
       <c r="K76" s="56"/>
       <c r="L76" s="60"/>
     </row>
-    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="120" t="s">
+    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="D77" s="119"/>
-      <c r="E77" s="119"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="119"/>
-      <c r="H77" s="119"/>
-      <c r="I77" s="114"/>
+      <c r="D77" s="113"/>
+      <c r="E77" s="113"/>
+      <c r="F77" s="113"/>
+      <c r="G77" s="113"/>
+      <c r="H77" s="113"/>
+      <c r="I77" s="110"/>
       <c r="J77" s="57"/>
       <c r="K77" s="58"/>
       <c r="L77" s="60"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" s="55"/>
       <c r="D78" s="59"/>
       <c r="E78" s="59"/>
@@ -2937,7 +3380,7 @@
       <c r="K78" s="58"/>
       <c r="L78" s="60"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" s="57" t="s">
         <v>47</v>
       </c>
@@ -2954,7 +3397,7 @@
       <c r="K79" s="58"/>
       <c r="L79" s="60"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C80" s="61"/>
       <c r="D80" s="62"/>
       <c r="E80" s="62"/>
@@ -2966,21 +3409,21 @@
       <c r="K80" s="58"/>
       <c r="L80" s="60"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="121" t="s">
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D81" s="122"/>
-      <c r="E81" s="122"/>
-      <c r="F81" s="122"/>
-      <c r="G81" s="122"/>
-      <c r="H81" s="122"/>
-      <c r="I81" s="123"/>
+      <c r="D81" s="116"/>
+      <c r="E81" s="116"/>
+      <c r="F81" s="116"/>
+      <c r="G81" s="116"/>
+      <c r="H81" s="116"/>
+      <c r="I81" s="117"/>
       <c r="J81" s="57"/>
       <c r="K81" s="58"/>
       <c r="L81" s="60"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C82" s="57"/>
       <c r="D82" s="60"/>
       <c r="E82" s="60"/>
@@ -2992,7 +3435,7 @@
       <c r="K82" s="58"/>
       <c r="L82" s="60"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C83" s="57" t="s">
         <v>49</v>
       </c>
@@ -3007,13 +3450,13 @@
       </c>
       <c r="H83" s="64"/>
       <c r="I83" s="58"/>
-      <c r="J83" s="124" t="s">
+      <c r="J83" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="K83" s="125"/>
+      <c r="K83" s="106"/>
       <c r="L83" s="73"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C84" s="57" t="s">
         <v>52</v>
       </c>
@@ -3032,7 +3475,7 @@
       <c r="K84" s="58"/>
       <c r="L84" s="60"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C85" s="57"/>
       <c r="D85" s="60"/>
       <c r="E85" s="60"/>
@@ -3040,11 +3483,11 @@
       <c r="G85" s="60"/>
       <c r="H85" s="60"/>
       <c r="I85" s="58"/>
-      <c r="J85" s="126"/>
-      <c r="K85" s="125"/>
+      <c r="J85" s="105"/>
+      <c r="K85" s="106"/>
       <c r="L85" s="73"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C86" s="57" t="s">
         <v>55</v>
       </c>
@@ -3054,14 +3497,14 @@
       <c r="G86" s="60"/>
       <c r="H86" s="70">
         <f>L$1/5</f>
-        <v>133587.01699999999</v>
+        <v>124104.827</v>
       </c>
       <c r="I86" s="58"/>
       <c r="J86" s="57"/>
       <c r="K86" s="58"/>
       <c r="L86" s="60"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C87" s="72" t="s">
         <v>38</v>
       </c>
@@ -3078,7 +3521,7 @@
       <c r="K87" s="58"/>
       <c r="L87" s="60"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" s="72" t="s">
         <v>36</v>
       </c>
@@ -3095,7 +3538,7 @@
       <c r="K88" s="58"/>
       <c r="L88" s="60"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C89" s="72" t="s">
         <v>39</v>
       </c>
@@ -3112,7 +3555,7 @@
       <c r="K89" s="58"/>
       <c r="L89" s="60"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="72" t="s">
         <v>37</v>
       </c>
@@ -3129,7 +3572,7 @@
       <c r="K90" s="58"/>
       <c r="L90" s="60"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D91" s="60"/>
       <c r="E91" s="60"/>
       <c r="F91" s="60"/>
@@ -3140,7 +3583,7 @@
       <c r="K91" s="58"/>
       <c r="L91" s="60"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C92" s="72" t="s">
         <v>43</v>
       </c>
@@ -3157,7 +3600,7 @@
       <c r="K92" s="67"/>
       <c r="L92" s="60"/>
     </row>
-    <row r="93" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D93" s="60"/>
       <c r="E93" s="60"/>
       <c r="F93" s="60"/>
@@ -3168,55 +3611,55 @@
       <c r="K93" s="58"/>
       <c r="L93" s="60"/>
     </row>
-    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="111" t="s">
+    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="D94" s="112"/>
-      <c r="E94" s="112"/>
-      <c r="F94" s="112"/>
-      <c r="G94" s="112"/>
-      <c r="H94" s="113">
+      <c r="D94" s="108"/>
+      <c r="E94" s="108"/>
+      <c r="F94" s="108"/>
+      <c r="G94" s="108"/>
+      <c r="H94" s="109">
         <f>SUM(H86:H93)</f>
-        <v>178953.3995</v>
-      </c>
-      <c r="I94" s="114"/>
+        <v>169471.2095</v>
+      </c>
+      <c r="I94" s="110"/>
       <c r="J94" s="68"/>
       <c r="K94" s="69"/>
       <c r="L94" s="60"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="118" t="s">
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D98" s="119"/>
-      <c r="E98" s="119"/>
-      <c r="F98" s="119"/>
-      <c r="G98" s="119"/>
-      <c r="H98" s="119"/>
-      <c r="I98" s="114"/>
+      <c r="D98" s="113"/>
+      <c r="E98" s="113"/>
+      <c r="F98" s="113"/>
+      <c r="G98" s="113"/>
+      <c r="H98" s="113"/>
+      <c r="I98" s="110"/>
       <c r="J98" s="55"/>
       <c r="K98" s="56"/>
       <c r="L98" s="60"/>
     </row>
-    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="120" t="s">
+    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="D99" s="119"/>
-      <c r="E99" s="119"/>
-      <c r="F99" s="119"/>
-      <c r="G99" s="119"/>
-      <c r="H99" s="119"/>
-      <c r="I99" s="114"/>
+      <c r="D99" s="113"/>
+      <c r="E99" s="113"/>
+      <c r="F99" s="113"/>
+      <c r="G99" s="113"/>
+      <c r="H99" s="113"/>
+      <c r="I99" s="110"/>
       <c r="J99" s="57"/>
       <c r="K99" s="58"/>
       <c r="L99" s="60"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C100" s="55"/>
       <c r="D100" s="59"/>
       <c r="E100" s="59"/>
@@ -3230,7 +3673,7 @@
       <c r="K100" s="58"/>
       <c r="L100" s="60"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C101" s="57" t="s">
         <v>47</v>
       </c>
@@ -3247,7 +3690,7 @@
       <c r="K101" s="58"/>
       <c r="L101" s="60"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C102" s="61"/>
       <c r="D102" s="62"/>
       <c r="E102" s="62"/>
@@ -3259,21 +3702,21 @@
       <c r="K102" s="58"/>
       <c r="L102" s="60"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="121" t="s">
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="D103" s="122"/>
-      <c r="E103" s="122"/>
-      <c r="F103" s="122"/>
-      <c r="G103" s="122"/>
-      <c r="H103" s="122"/>
-      <c r="I103" s="123"/>
+      <c r="D103" s="116"/>
+      <c r="E103" s="116"/>
+      <c r="F103" s="116"/>
+      <c r="G103" s="116"/>
+      <c r="H103" s="116"/>
+      <c r="I103" s="117"/>
       <c r="J103" s="57"/>
       <c r="K103" s="58"/>
       <c r="L103" s="60"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C104" s="57"/>
       <c r="D104" s="60"/>
       <c r="E104" s="60"/>
@@ -3285,7 +3728,7 @@
       <c r="K104" s="58"/>
       <c r="L104" s="60"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C105" s="57" t="s">
         <v>49</v>
       </c>
@@ -3300,13 +3743,13 @@
       </c>
       <c r="H105" s="64"/>
       <c r="I105" s="58"/>
-      <c r="J105" s="124" t="s">
+      <c r="J105" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="K105" s="125"/>
+      <c r="K105" s="106"/>
       <c r="L105" s="73"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C106" s="57" t="s">
         <v>52</v>
       </c>
@@ -3324,7 +3767,7 @@
       <c r="K106" s="58"/>
       <c r="L106" s="60"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" s="57"/>
       <c r="D107" s="60"/>
       <c r="E107" s="60"/>
@@ -3332,11 +3775,11 @@
       <c r="G107" s="60"/>
       <c r="H107" s="60"/>
       <c r="I107" s="58"/>
-      <c r="J107" s="126"/>
-      <c r="K107" s="125"/>
+      <c r="J107" s="105"/>
+      <c r="K107" s="106"/>
       <c r="L107" s="73"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" s="57" t="s">
         <v>55</v>
       </c>
@@ -3346,14 +3789,14 @@
       <c r="G108" s="60"/>
       <c r="H108" s="70">
         <f>L$1/5</f>
-        <v>133587.01699999999</v>
+        <v>124104.827</v>
       </c>
       <c r="I108" s="58"/>
       <c r="J108" s="57"/>
       <c r="K108" s="58"/>
       <c r="L108" s="60"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C109" s="72" t="s">
         <v>38</v>
       </c>
@@ -3370,7 +3813,7 @@
       <c r="K109" s="58"/>
       <c r="L109" s="60"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" s="72" t="s">
         <v>36</v>
       </c>
@@ -3387,7 +3830,7 @@
       <c r="K110" s="58"/>
       <c r="L110" s="60"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" s="72" t="s">
         <v>39</v>
       </c>
@@ -3404,7 +3847,7 @@
       <c r="K111" s="58"/>
       <c r="L111" s="60"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" s="72" t="s">
         <v>37</v>
       </c>
@@ -3421,7 +3864,7 @@
       <c r="K112" s="58"/>
       <c r="L112" s="60"/>
     </row>
-    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D113" s="60"/>
       <c r="E113" s="60"/>
       <c r="F113" s="60"/>
@@ -3432,7 +3875,7 @@
       <c r="K113" s="58"/>
       <c r="L113" s="60"/>
     </row>
-    <row r="114" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" s="72" t="s">
         <v>43</v>
       </c>
@@ -3449,7 +3892,7 @@
       <c r="K114" s="67"/>
       <c r="L114" s="60"/>
     </row>
-    <row r="115" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D115" s="60"/>
       <c r="E115" s="60"/>
       <c r="F115" s="60"/>
@@ -3460,50 +3903,27 @@
       <c r="K115" s="58"/>
       <c r="L115" s="60"/>
     </row>
-    <row r="116" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="111" t="s">
+    <row r="116" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="D116" s="112"/>
-      <c r="E116" s="112"/>
-      <c r="F116" s="112"/>
-      <c r="G116" s="112"/>
-      <c r="H116" s="113">
+      <c r="D116" s="108"/>
+      <c r="E116" s="108"/>
+      <c r="F116" s="108"/>
+      <c r="G116" s="108"/>
+      <c r="H116" s="109">
         <f>SUM(H108:H115)</f>
-        <v>178953.3995</v>
-      </c>
-      <c r="I116" s="114"/>
+        <v>169471.2095</v>
+      </c>
+      <c r="I116" s="110"/>
       <c r="J116" s="68"/>
       <c r="K116" s="69"/>
       <c r="L116" s="60"/>
     </row>
-    <row r="117" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="117" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3520,449 +3940,32 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="78" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:G66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="127" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="128"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="105">
-        <v>71833</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="31">
-        <v>-750223.00791600638</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="105">
-        <v>4519.7749999999996</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="101" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="102">
-        <f>'prorrateo '!F10</f>
-        <v>759494.33010000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="52"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="101" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="103">
-        <f>-C26</f>
-        <v>-608927.53500000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="131">
-        <v>95606.720000000001</v>
-      </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="103"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="131">
-        <v>140555</v>
-      </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="104"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="132">
-        <v>28281.4</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="104"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="105">
-        <v>66605.47</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="104"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="132">
-        <v>157756.17000000001</v>
-      </c>
-      <c r="E19" s="101"/>
-      <c r="F19" s="104"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="105">
-        <v>23770</v>
-      </c>
-      <c r="E20" s="101"/>
-      <c r="F20" s="104"/>
-    </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="74">
-        <f>SUM(C12:C20)</f>
-        <v>588927.53500000003</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="33">
-        <f>SUM(F12:F19)</f>
-        <v>-599656.21281600639</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="131">
-        <v>20000</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="130" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="130"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="52"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="44">
-        <f>SUM(C22:C24)</f>
-        <v>20000</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="130"/>
-      <c r="F25" s="130"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="75">
-        <f>+C25+C21</f>
-        <v>608927.53500000003</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="130"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="76"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="25"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="77"/>
-      <c r="E29" s="130"/>
-      <c r="F29" s="130"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="29"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="78">
-        <v>0</v>
-      </c>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="78">
-        <v>0</v>
-      </c>
-      <c r="E31" s="130"/>
-      <c r="F31" s="130"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="79"/>
-      <c r="E32" s="130"/>
-      <c r="F32" s="130"/>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="129"/>
-      <c r="B33" s="129"/>
-      <c r="C33" s="78"/>
-      <c r="E33" s="130"/>
-      <c r="F33" s="130"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="29"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="78">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="50">
-        <f>SUM(C30:C34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C36" s="78"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="80">
-        <f>C36+C26</f>
-        <v>608927.53500000003</v>
-      </c>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="50">
-        <f>+C26+C35</f>
-        <v>608927.53500000003</v>
-      </c>
-      <c r="E38" s="10"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D46" s="10"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D47" s="10"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="13"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="E23:F33"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId2"/>
-  <drawing r:id="rId3"/>
-</worksheet>
 </file>